--- a/Ahmedabad-March-2026.xlsx
+++ b/Ahmedabad-March-2026.xlsx
@@ -187,7 +187,7 @@
     <t>AMAZE</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>CITROEN</t>
@@ -202,7 +202,7 @@
     <t>ERTIGA</t>
   </si>
   <si>
-    <t>TEMPO TRAVEL</t>
+    <t>TEMPO TRAVELLER</t>
   </si>
   <si>
     <t>15/05/2025</t>
